--- a/dept/file/dept_adv.xlsx
+++ b/dept/file/dept_adv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\대학성과관리팀\4 행정부서 및 학과 연간운영계획서 총괄\2025 (평가기준 학년도  2024학년도)\4.평가자료 수합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DONGGYUN\Documents\GitHub\dhcpm.github.io\dept\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBEF7351-37C8-4A91-A67F-F8705BC426FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A440CF7F-A251-48C0-ACF3-786F1F14F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1194,6 +1194,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D182"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2245,7 +2251,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>44</v>
       </c>
@@ -2259,7 +2265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>47</v>
       </c>
@@ -2273,7 +2279,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2287,7 +2293,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2307,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -2315,7 +2321,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -2329,7 +2335,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -2343,7 +2349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -2357,7 +2363,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -2371,7 +2377,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -2385,7 +2391,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>55</v>
       </c>
@@ -2399,7 +2405,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>22</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>24</v>
       </c>
@@ -2427,7 +2433,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -2441,7 +2447,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>59</v>
       </c>
@@ -2469,7 +2475,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -2497,7 +2503,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>33</v>
       </c>
@@ -2525,7 +2531,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>37</v>
       </c>
@@ -2539,7 +2545,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>39</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -2567,7 +2573,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>62</v>
       </c>
@@ -2581,7 +2587,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -2595,7 +2601,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -3365,7 +3371,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>44</v>
       </c>
@@ -3379,7 +3385,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>47</v>
       </c>
@@ -3393,7 +3399,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -3407,7 +3413,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" ht="396.75" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>8</v>
       </c>
@@ -3421,7 +3427,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -3435,7 +3441,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" ht="327.75" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>12</v>
       </c>
@@ -3449,7 +3455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" ht="276" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>14</v>
       </c>
@@ -3463,7 +3469,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="310.5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>53</v>
       </c>
@@ -3477,7 +3483,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -3491,7 +3497,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="396.75" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -3505,7 +3511,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" ht="224.25" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>20</v>
       </c>
@@ -3519,7 +3525,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" ht="276" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>55</v>
       </c>
@@ -3533,7 +3539,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="258.75" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>22</v>
       </c>
@@ -3547,7 +3553,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="293.25" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>24</v>
       </c>
@@ -3561,7 +3567,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="293.25" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>26</v>
       </c>
@@ -3575,7 +3581,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="258.75" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>28</v>
       </c>
@@ -3603,7 +3609,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="241.5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>29</v>
       </c>
@@ -3631,7 +3637,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="310.5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -3645,7 +3651,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="224.25" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -3673,7 +3679,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="293.25" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -3687,7 +3693,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" ht="276" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -3701,7 +3707,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" ht="362.25" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>62</v>
       </c>
